--- a/docs/triton-learning/cards/triton-lesson-02-fused-softmax-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-02-fused-softmax-correction.xlsx
@@ -41,17 +41,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100% occupancy 等于执行单元全忙吗？</t>
+          <t xml:space="preserve">分析 GPU kernel 性能时，若 occupancy 达到 100%，是否就能判断计算执行单元都在忙？occupancy 实际描述哪一种“占满”？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">解释 GPU 的 warp 驻留容量</t>
+          <t xml:space="preserve">复习 GPU 的 warp 驻留指标：occupancy 比较每个 SM 上已驻留的 active warps 与硬件最多可驻留的 warps。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">只说明 warp 驻留容量已满，不能据此断言执行单元都在工作。</t>
+          <t xml:space="preserve">100% 表示 warp 驻留容量已满，不能据此判断执行单元始终都在工作。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -61,9 +61,10 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：驻留状态与实际发射、执行状态不同。
-• [T#B#原因]：等待访存或依赖的 stalled warp 仍计入 active warps。
-[T#B,!c47f17#边界]：高 occupancy 不保证最佳性能；不要用驻留容量代替执行单元忙碌程度。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：occupancy 衡量驻留容量的利用程度，不直接衡量这一时刻有多少计算指令正在执行。
+• [T#B#为何会不同]：一个 warp 可以已经驻留，却因等待内存数据或前序指令结果而暂停推进。这类 stalled warp 仍计入 active warps。
+• [T#B#状态层次]：active 表示已驻留；eligible 表示当时有可调度的就绪指令；issued 表示指令实际被发射。驻留并不自动意味着后两种状态。
+[T#B,!c47f17#边界]：高 occupancy 可能帮助隐藏延迟，但不能单独证明最佳性能，更不能把 100% occupancy 直接翻译成“所有计算单元一直满负荷”。</t>
         </is>
       </c>
     </row>

--- a/docs/triton-learning/cards/triton-lesson-02-fused-softmax-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-02-fused-softmax-correction.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -41,33 +41,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">分析 GPU kernel 性能时，若 occupancy 达到 100%，是否就能判断计算执行单元都在忙？occupancy 实际描述哪一种“占满”？</t>
+          <t xml:space="preserve">Triton 3.7.1 的 persistent softmax 增大 tl.range 行循环的 num_stages 后，若每个 program 因此占用更多寄存器或共享内存，最先受影响的是什么？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">复习 GPU 的 warp 驻留指标：occupancy 比较每个 SM 上已驻留的 active warps 与硬件最多可驻留的 warps。</t>
+          <t xml:space="preserve">同一个 kernel 只改变 num_stages；编译结果显示每个 program 的资源用量上升。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100% 表示 warp 驻留容量已满，不能据此判断执行单元始终都在工作。</t>
+          <t xml:space="preserve">最先受影响的是每个 SM 能同时驻留的 program 数：资源压力通常先减少并行驻留，而不是直接让单个 stage 变慢；只有出现 spilling 等机制，才谈得上单个 program 变慢，且需要相应证据。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">只能说计算单元全都在被用，但不一定用得好</t>
+          <t xml:space="preserve">如果资源不足，会拖慢单个stage的耗时，进而拖慢整体耗时</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：occupancy 衡量驻留容量的利用程度，不直接衡量这一时刻有多少计算指令正在执行。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错在因果的落点：资源随在途工作增加而上升这一前提没错，但这些资源限制的是 SM 能同时容纳多少个 program，而不是某个 stage 自身跑多快。
+• [T#B#驻留容量]：每个 SM 的寄存器和共享内存总量固定；每个 program 占得越多，能同时驻留的 program 越少，并行度随之下降，整体才可能变慢。
+• [T#B#何时才是单个变慢]：若资源放不下而发生 spilling，单个 program 才可能变慢；要这样下结论，需要 spilling 的证据。
+[T#B,!c47f17#边界]：stages=4 也不保证保存四个完整行，不保证寄存器与共享内存同时增长；结论以实际编译特化的资源记录为准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">分析 GPU kernel 性能时，profiler 报告某 kernel 的 occupancy 为 100%。这个 100% 准确地说明了哪一种“占满”？</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">只讨论 occupancy 这一项读数本身能说明什么。</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% 只说明 warp 驻留容量已满：每个 SM 上驻留的 active warps 达到硬件上限；这些 warp 可能在等待数据，不能据此断定执行单元都在工作。</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">只能说计算单元全都在被用，但不一定用得好</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：原答“不一定用得好”（不能推出最佳性能）是对的；错在“计算单元全都在被用”：occupancy 衡量的是驻留容量的占用，不是执行单元有多忙。
 • [T#B#为何会不同]：一个 warp 可以已经驻留，却因等待内存数据或前序指令结果而暂停推进。这类 stalled warp 仍计入 active warps。
 • [T#B#状态层次]：active 表示已驻留；eligible 表示当时有可调度的就绪指令；issued 表示指令实际被发射。驻留并不自动意味着后两种状态。
 [T#B,!c47f17#边界]：高 occupancy 可能帮助隐藏延迟，但不能单独证明最佳性能，更不能把 100% occupancy 直接翻译成“所有计算单元一直满负荷”。</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">persistent softmax 有 M 行，program p 依次处理 p、p+P、p+2P… 行（P 为实际启动的 program 数）。若实际启动 P=M，增大 tl.range 行循环的 num_stages 能带来什么样的重叠？</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton 3.7.1；行循环写作 for row in tl.range(pid, M, P, num_stages=s)。</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同一 program 内没有可流水的重叠：P=M 时每个 program 只有一次行迭代，没有自己的下一行；不同 program 的交错执行属于硬件调度，不是 tl.range(num_stages) 的跨迭代流水。</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">如果能够在前一批program进行计算处理时，预先启动后一批program开始读取数据，也有可能实现软件流水</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错在把两种不同层次的重叠混为一谈：num_stages 的作用域是同一个 program 内行循环的不同迭代，原答描述的却是不同 program 之间的交错。
+• [T#B#按行号推导]：program p 第一次处理行 p，下一次的行号是 p+M，已不小于 M，循环立即结束，所以每个 program 只有一次迭代。
+• [T#B#硬件调度]：GPU 可能让不同 program 交错执行，一个在计算时另一个在读数据，但这是硬件对独立 program 的调度，不属于某个 program 行循环内部的流水。
+[T#B,!c47f17#边界]：要让 num_stages 有可流水的对象，同一 program 必须有多次迭代，例如 P 小于 M、每个 program 处理多行。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>